--- a/data/3.meta_data/matrices/0080a.xlsx
+++ b/data/3.meta_data/matrices/0080a.xlsx
@@ -1,21 +1,75 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/3.meta_data/matrices/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_6D6BFDCE8F79A8D366075C52F3844A371C4FF79B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89A4BA4D-945A-46F3-9ED5-5B3B48818422}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>srlstrategies</t>
+  </si>
+  <si>
+    <t>academicselfefficacy</t>
+  </si>
+  <si>
+    <t>academicsatisfaction</t>
+  </si>
+  <si>
+    <t>selfmanagement</t>
+  </si>
+  <si>
+    <t>socialengagement</t>
+  </si>
+  <si>
+    <t>cooperation</t>
+  </si>
+  <si>
+    <t>emotionalresilience</t>
+  </si>
+  <si>
+    <t>innovation</t>
+  </si>
+  <si>
+    <t>academicachievement</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -59,17 +113,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +169,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +203,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +238,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,132 +414,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>srlstrategies</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>academicselfefficacy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>academicsatisfaction</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>selfmanagement</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>socialengagement</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cooperation</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>emotionalresilience</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>innovation</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>academicachievement</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>sex</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.4678753950824326</v>
+        <v>0.46787539508243259</v>
       </c>
       <c r="C2">
-        <v>0.3251826833125769</v>
+        <v>0.32518268331257688</v>
       </c>
       <c r="D2">
-        <v>0.4347691948229001</v>
+        <v>0.43476919482290011</v>
       </c>
       <c r="E2">
-        <v>0.3413427741827634</v>
+        <v>0.34134277418276338</v>
       </c>
       <c r="F2">
-        <v>0.2200361070098487</v>
+        <v>0.22003610700984871</v>
       </c>
       <c r="G2">
-        <v>0.2266590082419102</v>
+        <v>0.22665900824191021</v>
       </c>
       <c r="H2">
-        <v>0.3225309986068023</v>
+        <v>0.32253099860680229</v>
       </c>
       <c r="I2">
-        <v>0.2808780128533402</v>
+        <v>0.28087801285334019</v>
       </c>
       <c r="J2">
-        <v>0.04645758107183325</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>4.6457581071833252E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.4678753950824326</v>
+        <v>0.46787539508243259</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0.4165522501235401</v>
+        <v>0.41655225012354008</v>
       </c>
       <c r="D3">
-        <v>0.5957502994256506</v>
+        <v>0.59575029942565061</v>
       </c>
       <c r="E3">
-        <v>0.5099288031117473</v>
+        <v>0.50992880311174726</v>
       </c>
       <c r="F3">
-        <v>0.4132392379259404</v>
+        <v>0.41323923792594042</v>
       </c>
       <c r="G3">
-        <v>0.3930905978301036</v>
+        <v>0.39309059783010358</v>
       </c>
       <c r="H3">
-        <v>0.4037893824882295</v>
+        <v>0.40378938248822949</v>
       </c>
       <c r="I3">
         <v>0.5130449408120934</v>
       </c>
       <c r="J3">
-        <v>0.04835137891372377</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>4.8351378913723771E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.3251826833125769</v>
+        <v>0.32518268331257688</v>
       </c>
       <c r="B4">
-        <v>0.4165522501235401</v>
+        <v>0.41655225012354008</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -484,13 +533,13 @@
         <v>0.3218670586777202</v>
       </c>
       <c r="E4">
-        <v>0.3429729815611784</v>
+        <v>0.34297298156117839</v>
       </c>
       <c r="F4">
         <v>0.287941989686476</v>
       </c>
       <c r="G4">
-        <v>0.2666184161153234</v>
+        <v>0.26661841611532339</v>
       </c>
       <c r="H4">
         <v>0.3325938421307833</v>
@@ -499,15 +548,15 @@
         <v>0.1412995898511461</v>
       </c>
       <c r="J4">
-        <v>0.02477904180121925</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>2.4779041801219249E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.4347691948229001</v>
+        <v>0.43476919482290011</v>
       </c>
       <c r="B5">
-        <v>0.5957502994256506</v>
+        <v>0.59575029942565061</v>
       </c>
       <c r="C5">
         <v>0.3218670586777202</v>
@@ -516,36 +565,36 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>0.4987536058562987</v>
+        <v>0.49875360585629869</v>
       </c>
       <c r="F5">
-        <v>0.4112158902189516</v>
+        <v>0.41121589021895161</v>
       </c>
       <c r="G5">
-        <v>0.4630780298543363</v>
+        <v>0.46307802985433633</v>
       </c>
       <c r="H5">
-        <v>0.4887643784498452</v>
+        <v>0.48876437844984522</v>
       </c>
       <c r="I5">
-        <v>0.4097496698568251</v>
+        <v>0.40974966985682509</v>
       </c>
       <c r="J5">
-        <v>0.07540136124880159</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>7.5401361248801591E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.3413427741827634</v>
+        <v>0.34134277418276338</v>
       </c>
       <c r="B6">
-        <v>0.5099288031117473</v>
+        <v>0.50992880311174726</v>
       </c>
       <c r="C6">
-        <v>0.3429729815611784</v>
+        <v>0.34297298156117839</v>
       </c>
       <c r="D6">
-        <v>0.4987536058562987</v>
+        <v>0.49875360585629869</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -554,30 +603,30 @@
         <v>0.6063934495806812</v>
       </c>
       <c r="G6">
-        <v>0.4737777442999984</v>
+        <v>0.47377774429999842</v>
       </c>
       <c r="H6">
-        <v>0.517252995752813</v>
+        <v>0.51725299575281303</v>
       </c>
       <c r="I6">
-        <v>0.3339854401853342</v>
+        <v>0.33398544018533421</v>
       </c>
       <c r="J6">
-        <v>0.02295711992983375</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>2.295711992983375E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.2200361070098487</v>
+        <v>0.22003610700984871</v>
       </c>
       <c r="B7">
-        <v>0.4132392379259404</v>
+        <v>0.41323923792594042</v>
       </c>
       <c r="C7">
         <v>0.287941989686476</v>
       </c>
       <c r="D7">
-        <v>0.4112158902189516</v>
+        <v>0.41121589021895161</v>
       </c>
       <c r="E7">
         <v>0.6063934495806812</v>
@@ -586,85 +635,85 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>0.6119387520279144</v>
+        <v>0.61193875202791437</v>
       </c>
       <c r="H7">
-        <v>0.4713173325255526</v>
+        <v>0.47131733252555258</v>
       </c>
       <c r="I7">
-        <v>0.2968543677387699</v>
+        <v>0.29685436773876989</v>
       </c>
       <c r="J7">
-        <v>0.07314249017970333</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>7.3142490179703326E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.2266590082419102</v>
+        <v>0.22665900824191021</v>
       </c>
       <c r="B8">
-        <v>0.3930905978301036</v>
+        <v>0.39309059783010358</v>
       </c>
       <c r="C8">
-        <v>0.2666184161153234</v>
+        <v>0.26661841611532339</v>
       </c>
       <c r="D8">
-        <v>0.4630780298543363</v>
+        <v>0.46307802985433633</v>
       </c>
       <c r="E8">
-        <v>0.4737777442999984</v>
+        <v>0.47377774429999842</v>
       </c>
       <c r="F8">
-        <v>0.6119387520279144</v>
+        <v>0.61193875202791437</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>0.5528025598544609</v>
+        <v>0.55280255985446092</v>
       </c>
       <c r="I8">
-        <v>0.2613720888626943</v>
+        <v>0.26137208886269431</v>
       </c>
       <c r="J8">
-        <v>-0.1101763000383637</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>-0.11017630003836371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.3225309986068023</v>
+        <v>0.32253099860680229</v>
       </c>
       <c r="B9">
-        <v>0.4037893824882295</v>
+        <v>0.40378938248822949</v>
       </c>
       <c r="C9">
         <v>0.3325938421307833</v>
       </c>
       <c r="D9">
-        <v>0.4887643784498452</v>
+        <v>0.48876437844984522</v>
       </c>
       <c r="E9">
-        <v>0.517252995752813</v>
+        <v>0.51725299575281303</v>
       </c>
       <c r="F9">
-        <v>0.4713173325255526</v>
+        <v>0.47131733252555258</v>
       </c>
       <c r="G9">
-        <v>0.5528025598544609</v>
+        <v>0.55280255985446092</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0.2449879959536252</v>
+        <v>0.24498799595362519</v>
       </c>
       <c r="J9">
-        <v>-0.05489924897864821</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>-5.4899248978648209E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.2808780128533402</v>
+        <v>0.28087801285334019</v>
       </c>
       <c r="B10">
         <v>0.5130449408120934</v>
@@ -673,19 +722,19 @@
         <v>0.1412995898511461</v>
       </c>
       <c r="D10">
-        <v>0.4097496698568251</v>
+        <v>0.40974966985682509</v>
       </c>
       <c r="E10">
-        <v>0.3339854401853342</v>
+        <v>0.33398544018533421</v>
       </c>
       <c r="F10">
-        <v>0.2968543677387699</v>
+        <v>0.29685436773876989</v>
       </c>
       <c r="G10">
-        <v>0.2613720888626943</v>
+        <v>0.26137208886269431</v>
       </c>
       <c r="H10">
-        <v>0.2449879959536252</v>
+        <v>0.24498799595362519</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -694,30 +743,30 @@
         <v>0.1099683433260414</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>0.04645758107183325</v>
+        <v>4.6457581071833252E-2</v>
       </c>
       <c r="B11">
-        <v>0.04835137891372377</v>
+        <v>4.8351378913723771E-2</v>
       </c>
       <c r="C11">
-        <v>0.02477904180121925</v>
+        <v>2.4779041801219249E-2</v>
       </c>
       <c r="D11">
-        <v>0.07540136124880159</v>
+        <v>7.5401361248801591E-2</v>
       </c>
       <c r="E11">
-        <v>0.02295711992983375</v>
+        <v>2.295711992983375E-2</v>
       </c>
       <c r="F11">
-        <v>0.07314249017970333</v>
+        <v>7.3142490179703326E-2</v>
       </c>
       <c r="G11">
-        <v>-0.1101763000383637</v>
+        <v>-0.11017630003836371</v>
       </c>
       <c r="H11">
-        <v>-0.05489924897864821</v>
+        <v>-5.4899248978648209E-2</v>
       </c>
       <c r="I11">
         <v>0.1099683433260414</v>
